--- a/data/trans_orig/P80_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P80_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>34176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22381</t>
+          <t>25224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42603</t>
+          <t>47559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>388130</t>
+          <t>391780</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371129</t>
+          <t>373617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396627</t>
+          <t>401392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>301213</t>
+          <t>349483</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290819</t>
+          <t>337288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307454</t>
+          <t>356282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>689343</t>
+          <t>741263</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670584</t>
+          <t>722746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>701354</t>
+          <t>753756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27796</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>42942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>408070</t>
+          <t>457536</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395751</t>
+          <t>443428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415670</t>
+          <t>466383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>502165</t>
+          <t>491584</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493041</t>
+          <t>484342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507083</t>
+          <t>496137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>910236</t>
+          <t>949121</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>894892</t>
+          <t>933972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919724</t>
+          <t>959869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510457</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510457</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510457</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934005</t>
+          <t>976914</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934005</t>
+          <t>976914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934005</t>
+          <t>976914</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>519474</t>
+          <t>601605</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509522</t>
+          <t>590278</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526654</t>
+          <t>609558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>533362</t>
+          <t>611412</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527212</t>
+          <t>604846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537514</t>
+          <t>615949</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1052836</t>
+          <t>1213017</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1042397</t>
+          <t>1200134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1061530</t>
+          <t>1222320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>29447</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35289</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>872615</t>
+          <t>682397</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>861033</t>
+          <t>673287</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880966</t>
+          <t>688934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>698993</t>
+          <t>720183</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>693045</t>
+          <t>712734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>703070</t>
+          <t>724810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1571608</t>
+          <t>1402580</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1560476</t>
+          <t>1390956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1582322</t>
+          <t>1410853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886104</t>
+          <t>698763</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886104</t>
+          <t>698763</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886104</t>
+          <t>698763</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709661</t>
+          <t>733264</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709661</t>
+          <t>733264</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709661</t>
+          <t>733264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1595765</t>
+          <t>1432027</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1595765</t>
+          <t>1432027</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1595765</t>
+          <t>1432027</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>554264</t>
+          <t>602009</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>548624</t>
+          <t>596233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>557847</t>
+          <t>605746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>541802</t>
+          <t>602209</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>536989</t>
+          <t>596397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>544701</t>
+          <t>605080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1096066</t>
+          <t>1204218</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089517</t>
+          <t>1197048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1101191</t>
+          <t>1209220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560303</t>
+          <t>608357</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560303</t>
+          <t>608357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560303</t>
+          <t>608357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>608166</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>608166</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>608166</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107577</t>
+          <t>1216523</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107577</t>
+          <t>1216523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107577</t>
+          <t>1216523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>502</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>366477</t>
+          <t>405321</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>363532</t>
+          <t>401992</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>367651</t>
+          <t>406578</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>603792</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>600570</t>
+          <t>430580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>605911</t>
+          <t>435837</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>970268</t>
+          <t>839419</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>966392</t>
+          <t>834968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973135</t>
+          <t>841804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>606294</t>
+          <t>436814</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606294</t>
+          <t>436814</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>606294</t>
+          <t>436814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974459</t>
+          <t>843893</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974459</t>
+          <t>843893</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974459</t>
+          <t>843893</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>424145</t>
+          <t>462835</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>421004</t>
+          <t>460029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>706904</t>
+          <t>773033</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>704402</t>
+          <t>770051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>60769</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88555</t>
+          <t>104966</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63275</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91253</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>141103</t>
+          <t>164756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3391790</t>
+          <t>3450847</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3368649</t>
+          <t>3424953</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3412246</t>
+          <t>3469150</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3605471</t>
+          <t>3671806</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3591344</t>
+          <t>3656141</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3618615</t>
+          <t>3683414</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6997261</t>
+          <t>7122653</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6970720</t>
+          <t>7092094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7020570</t>
+          <t>7146288</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
